--- a/reports/scan_report.xlsx
+++ b/reports/scan_report.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="29">
   <si>
     <t>dataset</t>
   </si>
@@ -43,6 +43,9 @@
     <t>Curated32</t>
   </si>
   <si>
+    <t>AtlasISIC31</t>
+  </si>
+  <si>
     <t>Psoriasis pictures Lichen Planus and related diseases</t>
   </si>
   <si>
@@ -77,6 +80,12 @@
   </si>
   <si>
     <t>32_CSD</t>
+  </si>
+  <si>
+    <t>Lichen Planus</t>
+  </si>
+  <si>
+    <t>Pityriasis Rosea</t>
   </si>
   <si>
     <t>SkinDisNet, SkinDisNet_2</t>
@@ -449,7 +458,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -477,7 +486,7 @@
         <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C2">
         <v>463</v>
@@ -486,10 +495,10 @@
         <v>6</v>
       </c>
       <c r="E2" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F2" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -497,7 +506,7 @@
         <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C3">
         <v>251</v>
@@ -506,10 +515,10 @@
         <v>6</v>
       </c>
       <c r="E3" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F3" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -517,7 +526,7 @@
         <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C4">
         <v>129</v>
@@ -526,10 +535,10 @@
         <v>6</v>
       </c>
       <c r="E4" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F4" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -537,7 +546,7 @@
         <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C5">
         <v>829</v>
@@ -546,10 +555,10 @@
         <v>6</v>
       </c>
       <c r="E5" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F5" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -557,7 +566,7 @@
         <v>6</v>
       </c>
       <c r="B6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C6">
         <v>85</v>
@@ -566,10 +575,10 @@
         <v>6</v>
       </c>
       <c r="E6" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F6" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -577,7 +586,7 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C7">
         <v>1714</v>
@@ -586,10 +595,10 @@
         <v>6</v>
       </c>
       <c r="E7" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F7" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -597,19 +606,19 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C8">
         <v>1120</v>
       </c>
       <c r="D8" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E8" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F8" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -617,19 +626,19 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C9">
         <v>7632</v>
       </c>
       <c r="D9" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E9" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F9" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -637,19 +646,19 @@
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C10">
         <v>7456</v>
       </c>
       <c r="D10" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E10" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F10" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -657,19 +666,19 @@
         <v>7</v>
       </c>
       <c r="B11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C11">
         <v>5488</v>
       </c>
       <c r="D11" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E11" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F11" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -677,19 +686,19 @@
         <v>7</v>
       </c>
       <c r="B12" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C12">
         <v>1264</v>
       </c>
       <c r="D12" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E12" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F12" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -697,19 +706,19 @@
         <v>7</v>
       </c>
       <c r="B13" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C13">
         <v>4400</v>
       </c>
       <c r="D13" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E13" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F13" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -717,7 +726,7 @@
         <v>8</v>
       </c>
       <c r="B14" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C14">
         <v>951</v>
@@ -726,10 +735,70 @@
         <v>8</v>
       </c>
       <c r="E14" t="s">
+        <v>26</v>
+      </c>
+      <c r="F14" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" t="s">
+        <v>9</v>
+      </c>
+      <c r="B15" t="s">
+        <v>22</v>
+      </c>
+      <c r="C15">
+        <v>132</v>
+      </c>
+      <c r="D15" t="s">
+        <v>9</v>
+      </c>
+      <c r="E15" t="s">
+        <v>25</v>
+      </c>
+      <c r="F15" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" t="s">
+        <v>9</v>
+      </c>
+      <c r="B16" t="s">
         <v>23</v>
       </c>
-      <c r="F14" t="s">
-        <v>24</v>
+      <c r="C16">
+        <v>129</v>
+      </c>
+      <c r="D16" t="s">
+        <v>9</v>
+      </c>
+      <c r="E16" t="s">
+        <v>25</v>
+      </c>
+      <c r="F16" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
+      <c r="A17" t="s">
+        <v>9</v>
+      </c>
+      <c r="B17" t="s">
+        <v>13</v>
+      </c>
+      <c r="C17">
+        <v>132</v>
+      </c>
+      <c r="D17" t="s">
+        <v>9</v>
+      </c>
+      <c r="E17" t="s">
+        <v>25</v>
+      </c>
+      <c r="F17" t="s">
+        <v>27</v>
       </c>
     </row>
   </sheetData>
